--- a/Lab6_Table.xlsx
+++ b/Lab6_Table.xlsx
@@ -439,32 +439,32 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>param1</t>
+          <t>Most Affected Parameter [mm]</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>value1_mm</t>
+          <t>Largest ERV Coordinate Change [mm]</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>param2</t>
+          <t>Second Most Affected Parameter [mm]</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>value2_mm</t>
+          <t>Second Largest ERV Coordinate Change [mm]</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>param3</t>
+          <t>Third Most Affected Parameter</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>value3_mm</t>
+          <t>Third Largest ERV Coordinate Change [mm]</t>
         </is>
       </c>
     </row>
